--- a/tame_output/ON/bt/strategyON_20231226.xlsx
+++ b/tame_output/ON/bt/strategyON_20231226.xlsx
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714846</v>
+        <v>3.147014107714845</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097102</v>
+        <v>3.163432091097101</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762262</v>
+        <v>3.169279212762261</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.18551435596348</v>
+        <v>3.185514355963479</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583694</v>
+        <v>3.199276732583693</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742724</v>
+        <v>3.238767863742723</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589524</v>
+        <v>3.260068416589523</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872957</v>
+        <v>3.306739876872956</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946329</v>
+        <v>3.312164595946328</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,7 +43025,7 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336486</v>
+        <v>3.300520058336485</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
@@ -43048,7 +43048,7 @@
         <v>45268</v>
       </c>
       <c r="B1806" t="n">
-        <v>3.318449829143339</v>
+        <v>3.318449829143338</v>
       </c>
       <c r="C1806" t="n">
         <v>3.100133560631823</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308503</v>
+        <v>3.311781349308502</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257516</v>
+        <v>3.271427670257515</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
@@ -43117,7 +43117,7 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.25296238744154</v>
+        <v>3.252962387441539</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
@@ -43140,7 +43140,7 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.241257540662168</v>
+        <v>3.241257540662167</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
@@ -43163,7 +43163,7 @@
         <v>45273</v>
       </c>
       <c r="B1811" t="n">
-        <v>3.285495323543324</v>
+        <v>3.285495323543323</v>
       </c>
       <c r="C1811" t="n">
         <v>3.132597942828719</v>
@@ -43186,7 +43186,7 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.287726162978608</v>
+        <v>3.287726162978607</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
@@ -43209,7 +43209,7 @@
         <v>45275</v>
       </c>
       <c r="B1813" t="n">
-        <v>3.275586179621267</v>
+        <v>3.275586179621266</v>
       </c>
       <c r="C1813" t="n">
         <v>3.128096071514691</v>
@@ -43232,7 +43232,7 @@
         <v>45276</v>
       </c>
       <c r="B1814" t="n">
-        <v>3.268822948291748</v>
+        <v>3.268822948291747</v>
       </c>
       <c r="C1814" t="n">
         <v>3.123696569025415</v>
@@ -43278,7 +43278,7 @@
         <v>45278</v>
       </c>
       <c r="B1816" t="n">
-        <v>3.291576855321623</v>
+        <v>3.291576855321622</v>
       </c>
       <c r="C1816" t="n">
         <v>3.127125924287274</v>
@@ -43301,7 +43301,7 @@
         <v>45279</v>
       </c>
       <c r="B1817" t="n">
-        <v>3.289048749923556</v>
+        <v>3.289048749923555</v>
       </c>
       <c r="C1817" t="n">
         <v>3.126153974671351</v>
@@ -43324,7 +43324,7 @@
         <v>45280</v>
       </c>
       <c r="B1818" t="n">
-        <v>3.3080721951607</v>
+        <v>3.308072195160699</v>
       </c>
       <c r="C1818" t="n">
         <v>3.115456695754193</v>
@@ -43347,7 +43347,7 @@
         <v>45281</v>
       </c>
       <c r="B1819" t="n">
-        <v>3.318993081823466</v>
+        <v>3.318993081823465</v>
       </c>
       <c r="C1819" t="n">
         <v>3.125373651216407</v>
@@ -43370,7 +43370,7 @@
         <v>45282</v>
       </c>
       <c r="B1820" t="n">
-        <v>3.305392684942104</v>
+        <v>3.305392684942103</v>
       </c>
       <c r="C1820" t="n">
         <v>3.132226628875955</v>
@@ -43393,7 +43393,7 @@
         <v>45283</v>
       </c>
       <c r="B1821" t="n">
-        <v>3.312076663414904</v>
+        <v>3.312076663414903</v>
       </c>
       <c r="C1821" t="n">
         <v>3.134450814492048</v>
@@ -43416,7 +43416,7 @@
         <v>45284</v>
       </c>
       <c r="B1822" t="n">
-        <v>3.296314293398914</v>
+        <v>3.296314293398913</v>
       </c>
       <c r="C1822" t="n">
         <v>3.121045839271831</v>
@@ -43445,16 +43445,16 @@
         <v>3.126711518797542</v>
       </c>
       <c r="D1823" t="n">
-        <v>0.1315726324466611</v>
+        <v>0.1316615649858486</v>
       </c>
       <c r="E1823" t="n">
-        <v>3.17898414746246</v>
+        <v>3.179019720478135</v>
       </c>
       <c r="F1823" t="n">
-        <v>1.783313344341171</v>
+        <v>1.783227539916611</v>
       </c>
       <c r="G1823" t="n">
-        <v>4.196699525402246</v>
+        <v>4.19664804274751</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231226.xlsx
+++ b/tame_output/ON/bt/strategyON_20231226.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>416.9%</t>
+          <t>416.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-129.3%</t>
+          <t>-129.2%</t>
         </is>
       </c>
     </row>
@@ -43445,16 +43445,16 @@
         <v>3.126711518797542</v>
       </c>
       <c r="D1823" t="n">
-        <v>0.1316615649858486</v>
+        <v>0.1318671944535614</v>
       </c>
       <c r="E1823" t="n">
-        <v>3.179019720478135</v>
+        <v>3.17910197226522</v>
       </c>
       <c r="F1823" t="n">
-        <v>1.783227539916611</v>
+        <v>1.783478981672065</v>
       </c>
       <c r="G1823" t="n">
-        <v>4.19664804274751</v>
+        <v>4.196798907800782</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231226.xlsx
+++ b/tame_output/ON/bt/strategyON_20231226.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>416.7%</t>
+          <t>466.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-129.2%</t>
+          <t>-139.3%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-28.5%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-38.9%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.3%</t>
+          <t>111.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>106.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>3.9%</t>
         </is>
       </c>
     </row>
@@ -43445,16 +43445,16 @@
         <v>3.126711518797542</v>
       </c>
       <c r="D1823" t="n">
-        <v>0.1318671944535614</v>
+        <v>0.03117611895072786</v>
       </c>
       <c r="E1823" t="n">
-        <v>3.17910197226522</v>
+        <v>3.138825542064086</v>
       </c>
       <c r="F1823" t="n">
-        <v>1.783478981672065</v>
+        <v>1.703970566136225</v>
       </c>
       <c r="G1823" t="n">
-        <v>4.196798907800782</v>
+        <v>4.149093858479278</v>
       </c>
     </row>
   </sheetData>
